--- a/data/keyboard.ranked.xlsx
+++ b/data/keyboard.ranked.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\projects\keyvolve\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABC65563-8C2A-4F09-8DC3-9AA12AA6D5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9649884F-2C23-4EF1-9A5F-F48C2A301F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="588" yWindow="-108" windowWidth="40800" windowHeight="17496" xr2:uid="{F3CD4031-8099-40E7-B2B1-CABB68E66095}"/>
   </bookViews>
   <sheets>
-    <sheet name="keyboard.ranked" sheetId="1" r:id="rId1"/>
+    <sheet name="1.0" sheetId="1" r:id="rId1"/>
+    <sheet name="0.8" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="23">
   <si>
     <t>from: Q (slot 0)</t>
   </si>
@@ -86,6 +87,9 @@
   </si>
   <si>
     <t>doubles:</t>
+  </si>
+  <si>
+    <t>summed-efforts:</t>
   </si>
 </sst>
 </file>
@@ -946,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D678AA6C-FE30-443D-BE0A-BF870F782909}">
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:AB94"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -3768,7 +3772,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>4.4000000000000004</v>
       </c>
@@ -3830,7 +3834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>5.52</v>
       </c>
@@ -3883,7 +3887,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -3903,7 +3907,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -3917,7 +3921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>10</v>
       </c>
@@ -3979,7 +3983,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>6.03</v>
       </c>
@@ -4041,7 +4045,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>7.04</v>
       </c>
@@ -4094,7 +4098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -4114,12 +4118,15 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="G91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>4.4000000000000004</v>
       </c>
@@ -4135,8 +4142,71 @@
       <c r="E92">
         <v>3.88</v>
       </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="G92">
+        <v>106.93</v>
+      </c>
+      <c r="H92">
+        <v>79.64</v>
+      </c>
+      <c r="I92">
+        <v>66.989999999999995</v>
+      </c>
+      <c r="J92">
+        <v>78.989999999999995</v>
+      </c>
+      <c r="K92">
+        <v>94.4</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92">
+        <v>2.11</v>
+      </c>
+      <c r="P92">
+        <v>2.7</v>
+      </c>
+      <c r="Q92">
+        <v>3.32</v>
+      </c>
+      <c r="R92">
+        <v>3.88</v>
+      </c>
+      <c r="S92">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="T92">
+        <v>4.99</v>
+      </c>
+      <c r="U92">
+        <v>5.52</v>
+      </c>
+      <c r="V92">
+        <v>6.03</v>
+      </c>
+      <c r="W92">
+        <v>6.55</v>
+      </c>
+      <c r="X92">
+        <v>7.04</v>
+      </c>
+      <c r="Y92">
+        <v>7.69</v>
+      </c>
+      <c r="Z92">
+        <v>8.34</v>
+      </c>
+      <c r="AA92">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="AB92">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>2.7</v>
       </c>
@@ -4152,8 +4222,71 @@
       <c r="E93">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="G93">
+        <v>74.98</v>
+      </c>
+      <c r="H93">
+        <v>63.73</v>
+      </c>
+      <c r="I93">
+        <v>59.35</v>
+      </c>
+      <c r="J93">
+        <v>60.29</v>
+      </c>
+      <c r="K93">
+        <v>80.040000000000006</v>
+      </c>
+      <c r="M93">
+        <v>0.8</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93">
+        <v>2.68</v>
+      </c>
+      <c r="P93">
+        <v>3.38</v>
+      </c>
+      <c r="Q93">
+        <v>4.05</v>
+      </c>
+      <c r="R93">
+        <v>4.62</v>
+      </c>
+      <c r="S93">
+        <v>5.13</v>
+      </c>
+      <c r="T93">
+        <v>5.69</v>
+      </c>
+      <c r="U93">
+        <v>6.19</v>
+      </c>
+      <c r="V93">
+        <v>6.65</v>
+      </c>
+      <c r="W93">
+        <v>7.11</v>
+      </c>
+      <c r="X93">
+        <v>7.54</v>
+      </c>
+      <c r="Y93">
+        <v>8.1</v>
+      </c>
+      <c r="Z93">
+        <v>8.64</v>
+      </c>
+      <c r="AA93">
+        <v>9.16</v>
+      </c>
+      <c r="AB93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>3.88</v>
       </c>
@@ -4169,9 +4302,120 @@
       <c r="E94">
         <v>3.88</v>
       </c>
+      <c r="G94">
+        <v>94.76</v>
+      </c>
+      <c r="H94">
+        <v>81.37</v>
+      </c>
+      <c r="I94">
+        <v>78.05</v>
+      </c>
+      <c r="J94">
+        <v>74.28</v>
+      </c>
+      <c r="K94">
+        <v>94.5</v>
+      </c>
+      <c r="M94">
+        <v>0.5</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94">
+        <v>4.16</v>
+      </c>
+      <c r="P94">
+        <v>4.92</v>
+      </c>
+      <c r="Q94">
+        <v>5.57</v>
+      </c>
+      <c r="R94">
+        <v>6.09</v>
+      </c>
+      <c r="S94">
+        <v>6.53</v>
+      </c>
+      <c r="T94">
+        <v>6.99</v>
+      </c>
+      <c r="U94">
+        <v>7.38</v>
+      </c>
+      <c r="V94">
+        <v>7.73</v>
+      </c>
+      <c r="W94">
+        <v>8.07</v>
+      </c>
+      <c r="X94">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="Y94">
+        <v>8.76</v>
+      </c>
+      <c r="Z94">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="AA94">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="AB94">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A92:E94">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A86:E88">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80:E82">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A74:E76">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68:E70">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -4183,7 +4427,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A86:E88">
+  <conditionalFormatting sqref="A62:E64">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -4195,7 +4439,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A80:E82">
+  <conditionalFormatting sqref="A56:E58">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50:E52">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -4207,7 +4463,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A74:E76">
+  <conditionalFormatting sqref="A44:E46">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4219,7 +4475,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A68:E70">
+  <conditionalFormatting sqref="A38:E40">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -4231,7 +4487,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:E64">
+  <conditionalFormatting sqref="A32:E34">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -4243,7 +4499,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A56:E58">
+  <conditionalFormatting sqref="A26:E28">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -4255,7 +4511,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A50:E52">
+  <conditionalFormatting sqref="A20:E22">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -4267,7 +4523,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44:E46">
+  <conditionalFormatting sqref="A14:E16">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -4279,7 +4535,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38:E40">
+  <conditionalFormatting sqref="A8:E10">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -4291,7 +4547,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:E34">
+  <conditionalFormatting sqref="A2:E4">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -4303,19 +4559,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:E28">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20:E22">
+  <conditionalFormatting sqref="G92:K94 M92:M94">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4327,7 +4571,3380 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14:E16">
+  <conditionalFormatting sqref="N92:AB92">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B9F24E4F-8F22-454E-8435-EECBF0DC59C5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N93:AB93">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3D28F6B1-EBC0-430E-BCCF-D8EB10C3D3FE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N94:AB94">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{EE8F6F80-8048-4BB2-80D2-6F3E4F163674}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B9F24E4F-8F22-454E-8435-EECBF0DC59C5}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N92:AB92</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3D28F6B1-EBC0-430E-BCCF-D8EB10C3D3FE}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N93:AB93</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{EE8F6F80-8048-4BB2-80D2-6F3E4F163674}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N94:AB94</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FD9BCA-9F08-4AD5-A16F-FA7B6064A05A}">
+  <dimension ref="A1:W94"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>5.13</v>
+      </c>
+      <c r="B2">
+        <v>7.11</v>
+      </c>
+      <c r="C2">
+        <v>6.19</v>
+      </c>
+      <c r="D2">
+        <v>6.19</v>
+      </c>
+      <c r="E2">
+        <v>7.54</v>
+      </c>
+      <c r="H2">
+        <v>1344</v>
+      </c>
+      <c r="I2">
+        <v>1533</v>
+      </c>
+      <c r="J2">
+        <v>1517</v>
+      </c>
+      <c r="K2">
+        <v>1148</v>
+      </c>
+      <c r="N2">
+        <v>95</v>
+      </c>
+      <c r="O2">
+        <v>102</v>
+      </c>
+      <c r="P2">
+        <v>98</v>
+      </c>
+      <c r="Q2">
+        <v>97</v>
+      </c>
+      <c r="T2">
+        <v>24</v>
+      </c>
+      <c r="U2">
+        <v>45</v>
+      </c>
+      <c r="V2">
+        <v>27</v>
+      </c>
+      <c r="W2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>8.64</v>
+      </c>
+      <c r="B3">
+        <v>7.54</v>
+      </c>
+      <c r="C3">
+        <v>7.54</v>
+      </c>
+      <c r="D3">
+        <v>6.65</v>
+      </c>
+      <c r="E3">
+        <v>7.54</v>
+      </c>
+      <c r="G3">
+        <v>943</v>
+      </c>
+      <c r="H3">
+        <v>1161</v>
+      </c>
+      <c r="I3">
+        <v>1210</v>
+      </c>
+      <c r="J3">
+        <v>1373</v>
+      </c>
+      <c r="K3">
+        <v>1186</v>
+      </c>
+      <c r="M3">
+        <v>96</v>
+      </c>
+      <c r="N3">
+        <v>98</v>
+      </c>
+      <c r="O3">
+        <v>98</v>
+      </c>
+      <c r="P3">
+        <v>91</v>
+      </c>
+      <c r="Q3">
+        <v>97</v>
+      </c>
+      <c r="S3">
+        <v>29</v>
+      </c>
+      <c r="T3">
+        <v>32</v>
+      </c>
+      <c r="U3">
+        <v>28</v>
+      </c>
+      <c r="V3">
+        <v>26</v>
+      </c>
+      <c r="W3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>9.16</v>
+      </c>
+      <c r="C4">
+        <v>8.64</v>
+      </c>
+      <c r="D4">
+        <v>8.1</v>
+      </c>
+      <c r="E4">
+        <v>9.16</v>
+      </c>
+      <c r="G4">
+        <v>508</v>
+      </c>
+      <c r="H4">
+        <v>788</v>
+      </c>
+      <c r="I4">
+        <v>919</v>
+      </c>
+      <c r="J4">
+        <v>1048</v>
+      </c>
+      <c r="K4">
+        <v>681</v>
+      </c>
+      <c r="M4">
+        <v>118</v>
+      </c>
+      <c r="N4">
+        <v>107</v>
+      </c>
+      <c r="O4">
+        <v>99</v>
+      </c>
+      <c r="P4">
+        <v>101</v>
+      </c>
+      <c r="Q4">
+        <v>106</v>
+      </c>
+      <c r="S4">
+        <v>47</v>
+      </c>
+      <c r="T4">
+        <v>48</v>
+      </c>
+      <c r="U4">
+        <v>34</v>
+      </c>
+      <c r="V4">
+        <v>34</v>
+      </c>
+      <c r="W4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>6.19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>7.86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>2</v>
+      </c>
+      <c r="S7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7.11</v>
+      </c>
+      <c r="B8">
+        <v>3.38</v>
+      </c>
+      <c r="C8">
+        <v>4.05</v>
+      </c>
+      <c r="D8">
+        <v>4.62</v>
+      </c>
+      <c r="E8">
+        <v>6.19</v>
+      </c>
+      <c r="G8">
+        <v>1329</v>
+      </c>
+      <c r="I8">
+        <v>2086</v>
+      </c>
+      <c r="J8">
+        <v>1953</v>
+      </c>
+      <c r="K8">
+        <v>1506</v>
+      </c>
+      <c r="M8">
+        <v>96</v>
+      </c>
+      <c r="O8">
+        <v>107</v>
+      </c>
+      <c r="P8">
+        <v>104</v>
+      </c>
+      <c r="Q8">
+        <v>96</v>
+      </c>
+      <c r="S8">
+        <v>26</v>
+      </c>
+      <c r="U8">
+        <v>48</v>
+      </c>
+      <c r="V8">
+        <v>30</v>
+      </c>
+      <c r="W8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>6.19</v>
+      </c>
+      <c r="B9">
+        <v>6.19</v>
+      </c>
+      <c r="C9">
+        <v>5.13</v>
+      </c>
+      <c r="D9">
+        <v>4.05</v>
+      </c>
+      <c r="E9">
+        <v>6.19</v>
+      </c>
+      <c r="G9">
+        <v>1562</v>
+      </c>
+      <c r="H9">
+        <v>1556</v>
+      </c>
+      <c r="I9">
+        <v>1780</v>
+      </c>
+      <c r="J9">
+        <v>2039</v>
+      </c>
+      <c r="K9">
+        <v>1519</v>
+      </c>
+      <c r="M9">
+        <v>98</v>
+      </c>
+      <c r="N9">
+        <v>94</v>
+      </c>
+      <c r="O9">
+        <v>102</v>
+      </c>
+      <c r="P9">
+        <v>108</v>
+      </c>
+      <c r="Q9">
+        <v>96</v>
+      </c>
+      <c r="S9">
+        <v>26</v>
+      </c>
+      <c r="T9">
+        <v>29</v>
+      </c>
+      <c r="U9">
+        <v>33</v>
+      </c>
+      <c r="V9">
+        <v>30</v>
+      </c>
+      <c r="W9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8.1</v>
+      </c>
+      <c r="B10">
+        <v>7.54</v>
+      </c>
+      <c r="C10">
+        <v>7.11</v>
+      </c>
+      <c r="D10">
+        <v>6.65</v>
+      </c>
+      <c r="E10">
+        <v>8.1</v>
+      </c>
+      <c r="G10">
+        <v>1072</v>
+      </c>
+      <c r="H10">
+        <v>1115</v>
+      </c>
+      <c r="I10">
+        <v>1287</v>
+      </c>
+      <c r="J10">
+        <v>1422</v>
+      </c>
+      <c r="K10">
+        <v>1065</v>
+      </c>
+      <c r="M10">
+        <v>107</v>
+      </c>
+      <c r="N10">
+        <v>103</v>
+      </c>
+      <c r="O10">
+        <v>98</v>
+      </c>
+      <c r="P10">
+        <v>92</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>46</v>
+      </c>
+      <c r="T10">
+        <v>30</v>
+      </c>
+      <c r="U10">
+        <v>30</v>
+      </c>
+      <c r="V10">
+        <v>28</v>
+      </c>
+      <c r="W10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>4.05</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>8.1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>6.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>2</v>
+      </c>
+      <c r="S13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>6.65</v>
+      </c>
+      <c r="B14">
+        <v>4.62</v>
+      </c>
+      <c r="C14">
+        <v>2.68</v>
+      </c>
+      <c r="D14">
+        <v>3.38</v>
+      </c>
+      <c r="E14">
+        <v>6.19</v>
+      </c>
+      <c r="G14">
+        <v>1454</v>
+      </c>
+      <c r="H14">
+        <v>1843</v>
+      </c>
+      <c r="J14">
+        <v>2186</v>
+      </c>
+      <c r="K14">
+        <v>1539</v>
+      </c>
+      <c r="M14">
+        <v>86</v>
+      </c>
+      <c r="N14">
+        <v>105</v>
+      </c>
+      <c r="P14">
+        <v>107</v>
+      </c>
+      <c r="Q14">
+        <v>90</v>
+      </c>
+      <c r="S14">
+        <v>44</v>
+      </c>
+      <c r="T14">
+        <v>30</v>
+      </c>
+      <c r="V14">
+        <v>49</v>
+      </c>
+      <c r="W14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>5.13</v>
+      </c>
+      <c r="B15">
+        <v>4.05</v>
+      </c>
+      <c r="C15">
+        <v>5.13</v>
+      </c>
+      <c r="D15">
+        <v>3.38</v>
+      </c>
+      <c r="E15">
+        <v>5.69</v>
+      </c>
+      <c r="G15">
+        <v>1818</v>
+      </c>
+      <c r="H15">
+        <v>2055</v>
+      </c>
+      <c r="I15">
+        <v>1827</v>
+      </c>
+      <c r="J15">
+        <v>2170</v>
+      </c>
+      <c r="K15">
+        <v>1655</v>
+      </c>
+      <c r="M15">
+        <v>90</v>
+      </c>
+      <c r="N15">
+        <v>104</v>
+      </c>
+      <c r="O15">
+        <v>99</v>
+      </c>
+      <c r="P15">
+        <v>107</v>
+      </c>
+      <c r="Q15">
+        <v>94</v>
+      </c>
+      <c r="S15">
+        <v>38</v>
+      </c>
+      <c r="T15">
+        <v>38</v>
+      </c>
+      <c r="U15">
+        <v>30</v>
+      </c>
+      <c r="V15">
+        <v>53</v>
+      </c>
+      <c r="W15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>7.11</v>
+      </c>
+      <c r="B16">
+        <v>6.65</v>
+      </c>
+      <c r="C16">
+        <v>6.65</v>
+      </c>
+      <c r="D16">
+        <v>5.69</v>
+      </c>
+      <c r="E16">
+        <v>7.11</v>
+      </c>
+      <c r="G16">
+        <v>1346</v>
+      </c>
+      <c r="H16">
+        <v>1461</v>
+      </c>
+      <c r="I16">
+        <v>1367</v>
+      </c>
+      <c r="J16">
+        <v>1615</v>
+      </c>
+      <c r="K16">
+        <v>1269</v>
+      </c>
+      <c r="M16">
+        <v>88</v>
+      </c>
+      <c r="N16">
+        <v>90</v>
+      </c>
+      <c r="O16">
+        <v>93</v>
+      </c>
+      <c r="P16">
+        <v>94</v>
+      </c>
+      <c r="Q16">
+        <v>92</v>
+      </c>
+      <c r="S16">
+        <v>29</v>
+      </c>
+      <c r="T16">
+        <v>40</v>
+      </c>
+      <c r="U16">
+        <v>23</v>
+      </c>
+      <c r="V16">
+        <v>29</v>
+      </c>
+      <c r="W16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>3.38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>7.11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>6.19</v>
+      </c>
+      <c r="B20">
+        <v>4.62</v>
+      </c>
+      <c r="C20">
+        <v>3.38</v>
+      </c>
+      <c r="D20">
+        <v>3.38</v>
+      </c>
+      <c r="E20">
+        <v>6.65</v>
+      </c>
+      <c r="G20">
+        <v>1549</v>
+      </c>
+      <c r="H20">
+        <v>1899</v>
+      </c>
+      <c r="I20">
+        <v>2189</v>
+      </c>
+      <c r="K20">
+        <v>1444</v>
+      </c>
+      <c r="M20">
+        <v>98</v>
+      </c>
+      <c r="N20">
+        <v>109</v>
+      </c>
+      <c r="O20">
+        <v>115</v>
+      </c>
+      <c r="Q20">
+        <v>93</v>
+      </c>
+      <c r="S20">
+        <v>26</v>
+      </c>
+      <c r="T20">
+        <v>32</v>
+      </c>
+      <c r="U20">
+        <v>46</v>
+      </c>
+      <c r="W20">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>5.69</v>
+      </c>
+      <c r="B21">
+        <v>4.62</v>
+      </c>
+      <c r="C21">
+        <v>5.69</v>
+      </c>
+      <c r="D21">
+        <v>5.69</v>
+      </c>
+      <c r="E21">
+        <v>6.65</v>
+      </c>
+      <c r="G21">
+        <v>1657</v>
+      </c>
+      <c r="H21">
+        <v>1849</v>
+      </c>
+      <c r="I21">
+        <v>1714</v>
+      </c>
+      <c r="J21">
+        <v>1656</v>
+      </c>
+      <c r="K21">
+        <v>1437</v>
+      </c>
+      <c r="M21">
+        <v>96</v>
+      </c>
+      <c r="N21">
+        <v>99</v>
+      </c>
+      <c r="O21">
+        <v>97</v>
+      </c>
+      <c r="P21">
+        <v>101</v>
+      </c>
+      <c r="Q21">
+        <v>96</v>
+      </c>
+      <c r="S21">
+        <v>27</v>
+      </c>
+      <c r="T21">
+        <v>31</v>
+      </c>
+      <c r="U21">
+        <v>29</v>
+      </c>
+      <c r="V21">
+        <v>31</v>
+      </c>
+      <c r="W21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>8.1</v>
+      </c>
+      <c r="B22">
+        <v>7.11</v>
+      </c>
+      <c r="C22">
+        <v>6.65</v>
+      </c>
+      <c r="D22">
+        <v>7.11</v>
+      </c>
+      <c r="E22">
+        <v>8.1</v>
+      </c>
+      <c r="G22">
+        <v>1047</v>
+      </c>
+      <c r="H22">
+        <v>1337</v>
+      </c>
+      <c r="I22">
+        <v>1418</v>
+      </c>
+      <c r="J22">
+        <v>1245</v>
+      </c>
+      <c r="K22">
+        <v>1082</v>
+      </c>
+      <c r="M22">
+        <v>103</v>
+      </c>
+      <c r="N22">
+        <v>92</v>
+      </c>
+      <c r="O22">
+        <v>93</v>
+      </c>
+      <c r="P22">
+        <v>98</v>
+      </c>
+      <c r="Q22">
+        <v>98</v>
+      </c>
+      <c r="S22">
+        <v>31</v>
+      </c>
+      <c r="T22">
+        <v>30</v>
+      </c>
+      <c r="U22">
+        <v>27</v>
+      </c>
+      <c r="V22">
+        <v>25</v>
+      </c>
+      <c r="W22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>3.38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>8.1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <v>6.16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>2</v>
+      </c>
+      <c r="S25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>7.11</v>
+      </c>
+      <c r="B26">
+        <v>6.19</v>
+      </c>
+      <c r="C26">
+        <v>5.69</v>
+      </c>
+      <c r="D26">
+        <v>7.11</v>
+      </c>
+      <c r="E26">
+        <v>4.62</v>
+      </c>
+      <c r="G26">
+        <v>1243</v>
+      </c>
+      <c r="H26">
+        <v>1584</v>
+      </c>
+      <c r="I26">
+        <v>1666</v>
+      </c>
+      <c r="J26">
+        <v>1241</v>
+      </c>
+      <c r="M26">
+        <v>93</v>
+      </c>
+      <c r="N26">
+        <v>98</v>
+      </c>
+      <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
+        <v>95</v>
+      </c>
+      <c r="S26">
+        <v>24</v>
+      </c>
+      <c r="T26">
+        <v>29</v>
+      </c>
+      <c r="U26">
+        <v>30</v>
+      </c>
+      <c r="V26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>6.65</v>
+      </c>
+      <c r="B27">
+        <v>6.19</v>
+      </c>
+      <c r="C27">
+        <v>6.19</v>
+      </c>
+      <c r="D27">
+        <v>7.11</v>
+      </c>
+      <c r="E27">
+        <v>7.54</v>
+      </c>
+      <c r="G27">
+        <v>1387</v>
+      </c>
+      <c r="H27">
+        <v>1478</v>
+      </c>
+      <c r="I27">
+        <v>1547</v>
+      </c>
+      <c r="J27">
+        <v>1333</v>
+      </c>
+      <c r="K27">
+        <v>1151</v>
+      </c>
+      <c r="M27">
+        <v>98</v>
+      </c>
+      <c r="N27">
+        <v>95</v>
+      </c>
+      <c r="O27">
+        <v>97</v>
+      </c>
+      <c r="P27">
+        <v>94</v>
+      </c>
+      <c r="Q27">
+        <v>96</v>
+      </c>
+      <c r="S27">
+        <v>27</v>
+      </c>
+      <c r="T27">
+        <v>27</v>
+      </c>
+      <c r="U27">
+        <v>26</v>
+      </c>
+      <c r="V27">
+        <v>25</v>
+      </c>
+      <c r="W27">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>9.16</v>
+      </c>
+      <c r="B28">
+        <v>8.1</v>
+      </c>
+      <c r="C28">
+        <v>7.54</v>
+      </c>
+      <c r="D28">
+        <v>8.64</v>
+      </c>
+      <c r="E28">
+        <v>8.64</v>
+      </c>
+      <c r="G28">
+        <v>706</v>
+      </c>
+      <c r="H28">
+        <v>1021</v>
+      </c>
+      <c r="I28">
+        <v>1216</v>
+      </c>
+      <c r="J28">
+        <v>936</v>
+      </c>
+      <c r="K28">
+        <v>820</v>
+      </c>
+      <c r="M28">
+        <v>112</v>
+      </c>
+      <c r="N28">
+        <v>98</v>
+      </c>
+      <c r="O28">
+        <v>95</v>
+      </c>
+      <c r="P28">
+        <v>105</v>
+      </c>
+      <c r="Q28">
+        <v>109</v>
+      </c>
+      <c r="S28">
+        <v>46</v>
+      </c>
+      <c r="T28">
+        <v>28</v>
+      </c>
+      <c r="U28">
+        <v>26</v>
+      </c>
+      <c r="V28">
+        <v>30</v>
+      </c>
+      <c r="W28">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>5.69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>9.16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>2</v>
+      </c>
+      <c r="S31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>9.16</v>
+      </c>
+      <c r="B32">
+        <v>6.65</v>
+      </c>
+      <c r="C32">
+        <v>5.13</v>
+      </c>
+      <c r="D32">
+        <v>6.19</v>
+      </c>
+      <c r="E32">
+        <v>7.11</v>
+      </c>
+      <c r="G32">
+        <v>762</v>
+      </c>
+      <c r="H32">
+        <v>1424</v>
+      </c>
+      <c r="I32">
+        <v>1751</v>
+      </c>
+      <c r="J32">
+        <v>1589</v>
+      </c>
+      <c r="K32">
+        <v>1318</v>
+      </c>
+      <c r="M32">
+        <v>144</v>
+      </c>
+      <c r="N32">
+        <v>97</v>
+      </c>
+      <c r="O32">
+        <v>101</v>
+      </c>
+      <c r="P32">
+        <v>90</v>
+      </c>
+      <c r="Q32">
+        <v>98</v>
+      </c>
+      <c r="S32">
+        <v>47</v>
+      </c>
+      <c r="T32">
+        <v>26</v>
+      </c>
+      <c r="U32">
+        <v>31</v>
+      </c>
+      <c r="V32">
+        <v>28</v>
+      </c>
+      <c r="W32">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>3.38</v>
+      </c>
+      <c r="B33">
+        <v>4.62</v>
+      </c>
+      <c r="C33">
+        <v>4.05</v>
+      </c>
+      <c r="D33">
+        <v>4.05</v>
+      </c>
+      <c r="E33">
+        <v>5.69</v>
+      </c>
+      <c r="H33">
+        <v>1866</v>
+      </c>
+      <c r="I33">
+        <v>2046</v>
+      </c>
+      <c r="J33">
+        <v>2043</v>
+      </c>
+      <c r="K33">
+        <v>1659</v>
+      </c>
+      <c r="N33">
+        <v>96</v>
+      </c>
+      <c r="O33">
+        <v>101</v>
+      </c>
+      <c r="P33">
+        <v>101</v>
+      </c>
+      <c r="Q33">
+        <v>93</v>
+      </c>
+      <c r="T33">
+        <v>27</v>
+      </c>
+      <c r="U33">
+        <v>53</v>
+      </c>
+      <c r="V33">
+        <v>30</v>
+      </c>
+      <c r="W33">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>8.1</v>
+      </c>
+      <c r="B34">
+        <v>6.65</v>
+      </c>
+      <c r="C34">
+        <v>6.19</v>
+      </c>
+      <c r="D34">
+        <v>5.13</v>
+      </c>
+      <c r="E34">
+        <v>6.65</v>
+      </c>
+      <c r="G34">
+        <v>957</v>
+      </c>
+      <c r="H34">
+        <v>1391</v>
+      </c>
+      <c r="I34">
+        <v>1504</v>
+      </c>
+      <c r="J34">
+        <v>1722</v>
+      </c>
+      <c r="K34">
+        <v>1461</v>
+      </c>
+      <c r="M34">
+        <v>121</v>
+      </c>
+      <c r="N34">
+        <v>97</v>
+      </c>
+      <c r="O34">
+        <v>93</v>
+      </c>
+      <c r="P34">
+        <v>98</v>
+      </c>
+      <c r="Q34">
+        <v>97</v>
+      </c>
+      <c r="S34">
+        <v>47</v>
+      </c>
+      <c r="T34">
+        <v>29</v>
+      </c>
+      <c r="U34">
+        <v>28</v>
+      </c>
+      <c r="V34">
+        <v>25</v>
+      </c>
+      <c r="W34">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35">
+        <v>4.05</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35">
+        <v>9.16</v>
+      </c>
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>2</v>
+      </c>
+      <c r="S37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>7.54</v>
+      </c>
+      <c r="B38">
+        <v>5.69</v>
+      </c>
+      <c r="C38">
+        <v>4.05</v>
+      </c>
+      <c r="D38">
+        <v>5.13</v>
+      </c>
+      <c r="E38">
+        <v>6.65</v>
+      </c>
+      <c r="G38">
+        <v>1199</v>
+      </c>
+      <c r="H38">
+        <v>1623</v>
+      </c>
+      <c r="I38">
+        <v>1983</v>
+      </c>
+      <c r="J38">
+        <v>1736</v>
+      </c>
+      <c r="K38">
+        <v>1407</v>
+      </c>
+      <c r="M38">
+        <v>129</v>
+      </c>
+      <c r="N38">
+        <v>93</v>
+      </c>
+      <c r="O38">
+        <v>95</v>
+      </c>
+      <c r="P38">
+        <v>96</v>
+      </c>
+      <c r="Q38">
+        <v>98</v>
+      </c>
+      <c r="S38">
+        <v>46</v>
+      </c>
+      <c r="T38">
+        <v>24</v>
+      </c>
+      <c r="U38">
+        <v>28</v>
+      </c>
+      <c r="V38">
+        <v>27</v>
+      </c>
+      <c r="W38">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>4.62</v>
+      </c>
+      <c r="B39">
+        <v>2.68</v>
+      </c>
+      <c r="C39">
+        <v>2.68</v>
+      </c>
+      <c r="D39">
+        <v>2.68</v>
+      </c>
+      <c r="E39">
+        <v>5.13</v>
+      </c>
+      <c r="G39">
+        <v>1937</v>
+      </c>
+      <c r="I39">
+        <v>2383</v>
+      </c>
+      <c r="J39">
+        <v>2289</v>
+      </c>
+      <c r="K39">
+        <v>1739</v>
+      </c>
+      <c r="M39">
+        <v>95</v>
+      </c>
+      <c r="O39">
+        <v>121</v>
+      </c>
+      <c r="P39">
+        <v>113</v>
+      </c>
+      <c r="Q39">
+        <v>94</v>
+      </c>
+      <c r="S39">
+        <v>32</v>
+      </c>
+      <c r="U39">
+        <v>46</v>
+      </c>
+      <c r="V39">
+        <v>47</v>
+      </c>
+      <c r="W39">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>5.69</v>
+      </c>
+      <c r="B40">
+        <v>5.13</v>
+      </c>
+      <c r="C40">
+        <v>5.13</v>
+      </c>
+      <c r="D40">
+        <v>4.05</v>
+      </c>
+      <c r="E40">
+        <v>6.65</v>
+      </c>
+      <c r="G40">
+        <v>1593</v>
+      </c>
+      <c r="H40">
+        <v>1722</v>
+      </c>
+      <c r="I40">
+        <v>1724</v>
+      </c>
+      <c r="J40">
+        <v>2014</v>
+      </c>
+      <c r="K40">
+        <v>1460</v>
+      </c>
+      <c r="M40">
+        <v>96</v>
+      </c>
+      <c r="N40">
+        <v>97</v>
+      </c>
+      <c r="O40">
+        <v>95</v>
+      </c>
+      <c r="P40">
+        <v>96</v>
+      </c>
+      <c r="Q40">
+        <v>103</v>
+      </c>
+      <c r="S40">
+        <v>26</v>
+      </c>
+      <c r="T40">
+        <v>24</v>
+      </c>
+      <c r="U40">
+        <v>28</v>
+      </c>
+      <c r="V40">
+        <v>29</v>
+      </c>
+      <c r="W40">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41">
+        <v>2.68</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>7.54</v>
+      </c>
+      <c r="E41" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1</v>
+      </c>
+      <c r="M43" t="s">
+        <v>2</v>
+      </c>
+      <c r="S43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>7.54</v>
+      </c>
+      <c r="B44">
+        <v>5.13</v>
+      </c>
+      <c r="C44">
+        <v>4.62</v>
+      </c>
+      <c r="D44">
+        <v>5.13</v>
+      </c>
+      <c r="E44">
+        <v>6.19</v>
+      </c>
+      <c r="G44">
+        <v>1221</v>
+      </c>
+      <c r="H44">
+        <v>1813</v>
+      </c>
+      <c r="I44">
+        <v>1869</v>
+      </c>
+      <c r="J44">
+        <v>1833</v>
+      </c>
+      <c r="K44">
+        <v>1499</v>
+      </c>
+      <c r="M44">
+        <v>131</v>
+      </c>
+      <c r="N44">
+        <v>89</v>
+      </c>
+      <c r="O44">
+        <v>92</v>
+      </c>
+      <c r="P44">
+        <v>91</v>
+      </c>
+      <c r="Q44">
+        <v>99</v>
+      </c>
+      <c r="S44">
+        <v>45</v>
+      </c>
+      <c r="T44">
+        <v>40</v>
+      </c>
+      <c r="U44">
+        <v>28</v>
+      </c>
+      <c r="V44">
+        <v>26</v>
+      </c>
+      <c r="W44">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>4.05</v>
+      </c>
+      <c r="B45">
+        <v>3.38</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>5.13</v>
+      </c>
+      <c r="G45">
+        <v>1974</v>
+      </c>
+      <c r="H45">
+        <v>2229</v>
+      </c>
+      <c r="J45">
+        <v>2596</v>
+      </c>
+      <c r="K45">
+        <v>1774</v>
+      </c>
+      <c r="M45">
+        <v>94</v>
+      </c>
+      <c r="N45">
+        <v>116</v>
+      </c>
+      <c r="P45">
+        <v>153</v>
+      </c>
+      <c r="Q45">
+        <v>93</v>
+      </c>
+      <c r="S45">
+        <v>26</v>
+      </c>
+      <c r="T45">
+        <v>45</v>
+      </c>
+      <c r="V45">
+        <v>45</v>
+      </c>
+      <c r="W45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>6.19</v>
+      </c>
+      <c r="B46">
+        <v>4.62</v>
+      </c>
+      <c r="C46">
+        <v>5.13</v>
+      </c>
+      <c r="D46">
+        <v>3.38</v>
+      </c>
+      <c r="E46">
+        <v>5.69</v>
+      </c>
+      <c r="G46">
+        <v>1587</v>
+      </c>
+      <c r="H46">
+        <v>1929</v>
+      </c>
+      <c r="I46">
+        <v>1816</v>
+      </c>
+      <c r="J46">
+        <v>2161</v>
+      </c>
+      <c r="K46">
+        <v>1656</v>
+      </c>
+      <c r="M46">
+        <v>95</v>
+      </c>
+      <c r="N46">
+        <v>96</v>
+      </c>
+      <c r="O46">
+        <v>87</v>
+      </c>
+      <c r="P46">
+        <v>101</v>
+      </c>
+      <c r="Q46">
+        <v>95</v>
+      </c>
+      <c r="S46">
+        <v>28</v>
+      </c>
+      <c r="T46">
+        <v>30</v>
+      </c>
+      <c r="U46">
+        <v>33</v>
+      </c>
+      <c r="V46">
+        <v>42</v>
+      </c>
+      <c r="W46">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>7.54</v>
+      </c>
+      <c r="E47" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1</v>
+      </c>
+      <c r="M49" t="s">
+        <v>2</v>
+      </c>
+      <c r="S49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>7.11</v>
+      </c>
+      <c r="B50">
+        <v>4.62</v>
+      </c>
+      <c r="C50">
+        <v>3.38</v>
+      </c>
+      <c r="D50">
+        <v>5.69</v>
+      </c>
+      <c r="E50">
+        <v>7.11</v>
+      </c>
+      <c r="G50">
+        <v>1263</v>
+      </c>
+      <c r="H50">
+        <v>1925</v>
+      </c>
+      <c r="I50">
+        <v>2107</v>
+      </c>
+      <c r="J50">
+        <v>1642</v>
+      </c>
+      <c r="K50">
+        <v>1249</v>
+      </c>
+      <c r="M50">
+        <v>101</v>
+      </c>
+      <c r="N50">
+        <v>96</v>
+      </c>
+      <c r="O50">
+        <v>101</v>
+      </c>
+      <c r="P50">
+        <v>97</v>
+      </c>
+      <c r="Q50">
+        <v>110</v>
+      </c>
+      <c r="S50">
+        <v>40</v>
+      </c>
+      <c r="T50">
+        <v>25</v>
+      </c>
+      <c r="U50">
+        <v>31</v>
+      </c>
+      <c r="V50">
+        <v>27</v>
+      </c>
+      <c r="W50">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>4.05</v>
+      </c>
+      <c r="B51">
+        <v>2.68</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>5.69</v>
+      </c>
+      <c r="G51">
+        <v>2030</v>
+      </c>
+      <c r="H51">
+        <v>2257</v>
+      </c>
+      <c r="I51">
+        <v>2529</v>
+      </c>
+      <c r="K51">
+        <v>1693</v>
+      </c>
+      <c r="M51">
+        <v>101</v>
+      </c>
+      <c r="N51">
+        <v>126</v>
+      </c>
+      <c r="O51">
+        <v>139</v>
+      </c>
+      <c r="Q51">
+        <v>95</v>
+      </c>
+      <c r="S51">
+        <v>30</v>
+      </c>
+      <c r="T51">
+        <v>49</v>
+      </c>
+      <c r="U51">
+        <v>47</v>
+      </c>
+      <c r="W51">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>6.19</v>
+      </c>
+      <c r="B52">
+        <v>5.13</v>
+      </c>
+      <c r="C52">
+        <v>4.62</v>
+      </c>
+      <c r="D52">
+        <v>5.13</v>
+      </c>
+      <c r="E52">
+        <v>6.65</v>
+      </c>
+      <c r="G52">
+        <v>1564</v>
+      </c>
+      <c r="H52">
+        <v>1831</v>
+      </c>
+      <c r="I52">
+        <v>1856</v>
+      </c>
+      <c r="J52">
+        <v>1779</v>
+      </c>
+      <c r="K52">
+        <v>1403</v>
+      </c>
+      <c r="M52">
+        <v>93</v>
+      </c>
+      <c r="N52">
+        <v>94</v>
+      </c>
+      <c r="O52">
+        <v>98</v>
+      </c>
+      <c r="P52">
+        <v>97</v>
+      </c>
+      <c r="Q52">
+        <v>90</v>
+      </c>
+      <c r="S52">
+        <v>32</v>
+      </c>
+      <c r="T52">
+        <v>27</v>
+      </c>
+      <c r="U52">
+        <v>24</v>
+      </c>
+      <c r="V52">
+        <v>25</v>
+      </c>
+      <c r="W52">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>7.11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>6</v>
+      </c>
+      <c r="F53">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1</v>
+      </c>
+      <c r="M55" t="s">
+        <v>2</v>
+      </c>
+      <c r="S55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>7.54</v>
+      </c>
+      <c r="B56">
+        <v>6.65</v>
+      </c>
+      <c r="C56">
+        <v>5.69</v>
+      </c>
+      <c r="D56">
+        <v>6.65</v>
+      </c>
+      <c r="E56">
+        <v>7.11</v>
+      </c>
+      <c r="G56">
+        <v>1180</v>
+      </c>
+      <c r="H56">
+        <v>1453</v>
+      </c>
+      <c r="I56">
+        <v>1653</v>
+      </c>
+      <c r="J56">
+        <v>1420</v>
+      </c>
+      <c r="K56">
+        <v>1235</v>
+      </c>
+      <c r="M56">
+        <v>88</v>
+      </c>
+      <c r="N56">
+        <v>88</v>
+      </c>
+      <c r="O56">
+        <v>89</v>
+      </c>
+      <c r="P56">
+        <v>83</v>
+      </c>
+      <c r="Q56">
+        <v>93</v>
+      </c>
+      <c r="S56">
+        <v>54</v>
+      </c>
+      <c r="T56">
+        <v>52</v>
+      </c>
+      <c r="U56">
+        <v>26</v>
+      </c>
+      <c r="V56">
+        <v>87</v>
+      </c>
+      <c r="W56">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>5.69</v>
+      </c>
+      <c r="B57">
+        <v>5.13</v>
+      </c>
+      <c r="C57">
+        <v>5.13</v>
+      </c>
+      <c r="D57">
+        <v>6.19</v>
+      </c>
+      <c r="E57">
+        <v>3.38</v>
+      </c>
+      <c r="G57">
+        <v>1658</v>
+      </c>
+      <c r="H57">
+        <v>1771</v>
+      </c>
+      <c r="I57">
+        <v>1833</v>
+      </c>
+      <c r="J57">
+        <v>1518</v>
+      </c>
+      <c r="M57">
+        <v>93</v>
+      </c>
+      <c r="N57">
+        <v>94</v>
+      </c>
+      <c r="O57">
+        <v>94</v>
+      </c>
+      <c r="P57">
+        <v>85</v>
+      </c>
+      <c r="S57">
+        <v>24</v>
+      </c>
+      <c r="T57">
+        <v>25</v>
+      </c>
+      <c r="U57">
+        <v>36</v>
+      </c>
+      <c r="V57">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>7.11</v>
+      </c>
+      <c r="B58">
+        <v>6.19</v>
+      </c>
+      <c r="C58">
+        <v>6.65</v>
+      </c>
+      <c r="D58">
+        <v>6.65</v>
+      </c>
+      <c r="E58">
+        <v>7.11</v>
+      </c>
+      <c r="G58">
+        <v>1320</v>
+      </c>
+      <c r="H58">
+        <v>1485</v>
+      </c>
+      <c r="I58">
+        <v>1456</v>
+      </c>
+      <c r="J58">
+        <v>1392</v>
+      </c>
+      <c r="K58">
+        <v>1344</v>
+      </c>
+      <c r="M58">
+        <v>95</v>
+      </c>
+      <c r="N58">
+        <v>89</v>
+      </c>
+      <c r="O58">
+        <v>80</v>
+      </c>
+      <c r="P58">
+        <v>92</v>
+      </c>
+      <c r="Q58">
+        <v>88</v>
+      </c>
+      <c r="S58">
+        <v>25</v>
+      </c>
+      <c r="T58">
+        <v>26</v>
+      </c>
+      <c r="U58">
+        <v>90</v>
+      </c>
+      <c r="V58">
+        <v>36</v>
+      </c>
+      <c r="W58">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>5.13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59">
+        <v>7.54</v>
+      </c>
+      <c r="E59" t="s">
+        <v>6</v>
+      </c>
+      <c r="F59">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1</v>
+      </c>
+      <c r="M61" t="s">
+        <v>2</v>
+      </c>
+      <c r="S61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>10</v>
+      </c>
+      <c r="B62">
+        <v>8.1</v>
+      </c>
+      <c r="C62">
+        <v>7.11</v>
+      </c>
+      <c r="D62">
+        <v>8.1</v>
+      </c>
+      <c r="E62">
+        <v>8.64</v>
+      </c>
+      <c r="G62">
+        <v>437</v>
+      </c>
+      <c r="H62">
+        <v>1057</v>
+      </c>
+      <c r="I62">
+        <v>1302</v>
+      </c>
+      <c r="J62">
+        <v>1083</v>
+      </c>
+      <c r="K62">
+        <v>900</v>
+      </c>
+      <c r="M62">
+        <v>153</v>
+      </c>
+      <c r="N62">
+        <v>101</v>
+      </c>
+      <c r="O62">
+        <v>98</v>
+      </c>
+      <c r="P62">
+        <v>104</v>
+      </c>
+      <c r="Q62">
+        <v>101</v>
+      </c>
+      <c r="S62">
+        <v>47</v>
+      </c>
+      <c r="T62">
+        <v>33</v>
+      </c>
+      <c r="U62">
+        <v>27</v>
+      </c>
+      <c r="V62">
+        <v>30</v>
+      </c>
+      <c r="W62">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>8.1</v>
+      </c>
+      <c r="B63">
+        <v>6.65</v>
+      </c>
+      <c r="C63">
+        <v>5.69</v>
+      </c>
+      <c r="D63">
+        <v>6.19</v>
+      </c>
+      <c r="E63">
+        <v>7.11</v>
+      </c>
+      <c r="G63">
+        <v>1050</v>
+      </c>
+      <c r="H63">
+        <v>1456</v>
+      </c>
+      <c r="I63">
+        <v>1641</v>
+      </c>
+      <c r="J63">
+        <v>1524</v>
+      </c>
+      <c r="K63">
+        <v>1260</v>
+      </c>
+      <c r="M63">
+        <v>100</v>
+      </c>
+      <c r="N63">
+        <v>97</v>
+      </c>
+      <c r="O63">
+        <v>97</v>
+      </c>
+      <c r="P63">
+        <v>97</v>
+      </c>
+      <c r="Q63">
+        <v>98</v>
+      </c>
+      <c r="S63">
+        <v>32</v>
+      </c>
+      <c r="T63">
+        <v>28</v>
+      </c>
+      <c r="U63">
+        <v>36</v>
+      </c>
+      <c r="V63">
+        <v>24</v>
+      </c>
+      <c r="W63">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>4.62</v>
+      </c>
+      <c r="B64">
+        <v>6.65</v>
+      </c>
+      <c r="C64">
+        <v>6.19</v>
+      </c>
+      <c r="D64">
+        <v>6.19</v>
+      </c>
+      <c r="E64">
+        <v>7.54</v>
+      </c>
+      <c r="H64">
+        <v>1441</v>
+      </c>
+      <c r="I64">
+        <v>1503</v>
+      </c>
+      <c r="J64">
+        <v>1544</v>
+      </c>
+      <c r="K64">
+        <v>1216</v>
+      </c>
+      <c r="N64">
+        <v>91</v>
+      </c>
+      <c r="O64">
+        <v>94</v>
+      </c>
+      <c r="P64">
+        <v>96</v>
+      </c>
+      <c r="Q64">
+        <v>101</v>
+      </c>
+      <c r="T64">
+        <v>26</v>
+      </c>
+      <c r="U64">
+        <v>24</v>
+      </c>
+      <c r="V64">
+        <v>24</v>
+      </c>
+      <c r="W64">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65">
+        <v>5.69</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1</v>
+      </c>
+      <c r="M67" t="s">
+        <v>2</v>
+      </c>
+      <c r="S67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>9.16</v>
+      </c>
+      <c r="B68">
+        <v>8.1</v>
+      </c>
+      <c r="C68">
+        <v>6.65</v>
+      </c>
+      <c r="D68">
+        <v>7.11</v>
+      </c>
+      <c r="E68">
+        <v>8.1</v>
+      </c>
+      <c r="G68">
+        <v>790</v>
+      </c>
+      <c r="H68">
+        <v>1009</v>
+      </c>
+      <c r="I68">
+        <v>1408</v>
+      </c>
+      <c r="J68">
+        <v>1346</v>
+      </c>
+      <c r="K68">
+        <v>1021</v>
+      </c>
+      <c r="M68">
+        <v>122</v>
+      </c>
+      <c r="N68">
+        <v>109</v>
+      </c>
+      <c r="O68">
+        <v>95</v>
+      </c>
+      <c r="P68">
+        <v>96</v>
+      </c>
+      <c r="Q68">
+        <v>104</v>
+      </c>
+      <c r="S68">
+        <v>46</v>
+      </c>
+      <c r="T68">
+        <v>30</v>
+      </c>
+      <c r="U68">
+        <v>24</v>
+      </c>
+      <c r="V68">
+        <v>27</v>
+      </c>
+      <c r="W68">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>7.11</v>
+      </c>
+      <c r="B69">
+        <v>6.19</v>
+      </c>
+      <c r="C69">
+        <v>4.62</v>
+      </c>
+      <c r="D69">
+        <v>5.13</v>
+      </c>
+      <c r="E69">
+        <v>6.19</v>
+      </c>
+      <c r="G69">
+        <v>1346</v>
+      </c>
+      <c r="H69">
+        <v>1534</v>
+      </c>
+      <c r="I69">
+        <v>1918</v>
+      </c>
+      <c r="J69">
+        <v>1822</v>
+      </c>
+      <c r="K69">
+        <v>1507</v>
+      </c>
+      <c r="M69">
+        <v>92</v>
+      </c>
+      <c r="N69">
+        <v>97</v>
+      </c>
+      <c r="O69">
+        <v>105</v>
+      </c>
+      <c r="P69">
+        <v>94</v>
+      </c>
+      <c r="Q69">
+        <v>93</v>
+      </c>
+      <c r="S69">
+        <v>25</v>
+      </c>
+      <c r="T69">
+        <v>24</v>
+      </c>
+      <c r="U69">
+        <v>46</v>
+      </c>
+      <c r="V69">
+        <v>46</v>
+      </c>
+      <c r="W69">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>6.19</v>
+      </c>
+      <c r="B70">
+        <v>4.05</v>
+      </c>
+      <c r="C70">
+        <v>5.13</v>
+      </c>
+      <c r="D70">
+        <v>5.13</v>
+      </c>
+      <c r="E70">
+        <v>7.11</v>
+      </c>
+      <c r="G70">
+        <v>1511</v>
+      </c>
+      <c r="I70">
+        <v>1817</v>
+      </c>
+      <c r="J70">
+        <v>1828</v>
+      </c>
+      <c r="K70">
+        <v>1288</v>
+      </c>
+      <c r="M70">
+        <v>95</v>
+      </c>
+      <c r="O70">
+        <v>95</v>
+      </c>
+      <c r="P70">
+        <v>97</v>
+      </c>
+      <c r="Q70">
+        <v>96</v>
+      </c>
+      <c r="S70">
+        <v>24</v>
+      </c>
+      <c r="U70">
+        <v>35</v>
+      </c>
+      <c r="V70">
+        <v>25</v>
+      </c>
+      <c r="W70">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71">
+        <v>4.62</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71">
+        <v>9.16</v>
+      </c>
+      <c r="E71" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1</v>
+      </c>
+      <c r="M73" t="s">
+        <v>2</v>
+      </c>
+      <c r="S73" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>8.64</v>
+      </c>
+      <c r="B74">
+        <v>6.65</v>
+      </c>
+      <c r="C74">
+        <v>7.11</v>
+      </c>
+      <c r="D74">
+        <v>6.65</v>
+      </c>
+      <c r="E74">
+        <v>7.54</v>
+      </c>
+      <c r="G74">
+        <v>847</v>
+      </c>
+      <c r="H74">
+        <v>1368</v>
+      </c>
+      <c r="I74">
+        <v>1283</v>
+      </c>
+      <c r="J74">
+        <v>1353</v>
+      </c>
+      <c r="K74">
+        <v>1100</v>
+      </c>
+      <c r="M74">
+        <v>121</v>
+      </c>
+      <c r="N74">
+        <v>97</v>
+      </c>
+      <c r="O74">
+        <v>97</v>
+      </c>
+      <c r="P74">
+        <v>90</v>
+      </c>
+      <c r="Q74">
+        <v>112</v>
+      </c>
+      <c r="S74">
+        <v>45</v>
+      </c>
+      <c r="T74">
+        <v>23</v>
+      </c>
+      <c r="U74">
+        <v>32</v>
+      </c>
+      <c r="V74">
+        <v>25</v>
+      </c>
+      <c r="W74">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>6.19</v>
+      </c>
+      <c r="B75">
+        <v>5.13</v>
+      </c>
+      <c r="C75">
+        <v>5.69</v>
+      </c>
+      <c r="D75">
+        <v>4.62</v>
+      </c>
+      <c r="E75">
+        <v>6.19</v>
+      </c>
+      <c r="G75">
+        <v>1527</v>
+      </c>
+      <c r="H75">
+        <v>1774</v>
+      </c>
+      <c r="I75">
+        <v>1697</v>
+      </c>
+      <c r="J75">
+        <v>1921</v>
+      </c>
+      <c r="K75">
+        <v>1532</v>
+      </c>
+      <c r="M75">
+        <v>97</v>
+      </c>
+      <c r="N75">
+        <v>99</v>
+      </c>
+      <c r="O75">
+        <v>98</v>
+      </c>
+      <c r="P75">
+        <v>98</v>
+      </c>
+      <c r="Q75">
+        <v>98</v>
+      </c>
+      <c r="S75">
+        <v>24</v>
+      </c>
+      <c r="T75">
+        <v>31</v>
+      </c>
+      <c r="U75">
+        <v>24</v>
+      </c>
+      <c r="V75">
+        <v>30</v>
+      </c>
+      <c r="W75">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>6.19</v>
+      </c>
+      <c r="B76">
+        <v>5.13</v>
+      </c>
+      <c r="C76">
+        <v>3.38</v>
+      </c>
+      <c r="D76">
+        <v>4.62</v>
+      </c>
+      <c r="E76">
+        <v>6.65</v>
+      </c>
+      <c r="G76">
+        <v>1519</v>
+      </c>
+      <c r="H76">
+        <v>1825</v>
+      </c>
+      <c r="J76">
+        <v>1949</v>
+      </c>
+      <c r="K76">
+        <v>1373</v>
+      </c>
+      <c r="M76">
+        <v>92</v>
+      </c>
+      <c r="N76">
+        <v>92</v>
+      </c>
+      <c r="P76">
+        <v>99</v>
+      </c>
+      <c r="Q76">
+        <v>93</v>
+      </c>
+      <c r="S76">
+        <v>30</v>
+      </c>
+      <c r="T76">
+        <v>31</v>
+      </c>
+      <c r="V76">
+        <v>30</v>
+      </c>
+      <c r="W76">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77">
+        <v>4.62</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77">
+        <v>8.64</v>
+      </c>
+      <c r="E77" t="s">
+        <v>6</v>
+      </c>
+      <c r="F77">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>2</v>
+      </c>
+      <c r="S79" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>8.64</v>
+      </c>
+      <c r="B80">
+        <v>6.65</v>
+      </c>
+      <c r="C80">
+        <v>5.69</v>
+      </c>
+      <c r="D80">
+        <v>7.54</v>
+      </c>
+      <c r="E80">
+        <v>8.1</v>
+      </c>
+      <c r="G80">
+        <v>901</v>
+      </c>
+      <c r="H80">
+        <v>1468</v>
+      </c>
+      <c r="I80">
+        <v>1640</v>
+      </c>
+      <c r="J80">
+        <v>1218</v>
+      </c>
+      <c r="K80">
+        <v>1002</v>
+      </c>
+      <c r="M80">
+        <v>111</v>
+      </c>
+      <c r="N80">
+        <v>93</v>
+      </c>
+      <c r="O80">
+        <v>97</v>
+      </c>
+      <c r="P80">
+        <v>108</v>
+      </c>
+      <c r="Q80">
+        <v>109</v>
+      </c>
+      <c r="S80">
+        <v>46</v>
+      </c>
+      <c r="T80">
+        <v>29</v>
+      </c>
+      <c r="U80">
+        <v>23</v>
+      </c>
+      <c r="V80">
+        <v>31</v>
+      </c>
+      <c r="W80">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>5.13</v>
+      </c>
+      <c r="B81">
+        <v>4.62</v>
+      </c>
+      <c r="C81">
+        <v>4.05</v>
+      </c>
+      <c r="D81">
+        <v>5.13</v>
+      </c>
+      <c r="E81">
+        <v>6.65</v>
+      </c>
+      <c r="G81">
+        <v>1809</v>
+      </c>
+      <c r="H81">
+        <v>1950</v>
+      </c>
+      <c r="I81">
+        <v>2053</v>
+      </c>
+      <c r="J81">
+        <v>1745</v>
+      </c>
+      <c r="K81">
+        <v>1387</v>
+      </c>
+      <c r="M81">
+        <v>82</v>
+      </c>
+      <c r="N81">
+        <v>98</v>
+      </c>
+      <c r="O81">
+        <v>108</v>
+      </c>
+      <c r="P81">
+        <v>92</v>
+      </c>
+      <c r="Q81">
+        <v>96</v>
+      </c>
+      <c r="S81">
+        <v>97</v>
+      </c>
+      <c r="T81">
+        <v>31</v>
+      </c>
+      <c r="U81">
+        <v>46</v>
+      </c>
+      <c r="V81">
+        <v>24</v>
+      </c>
+      <c r="W81">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>6.19</v>
+      </c>
+      <c r="B82">
+        <v>5.13</v>
+      </c>
+      <c r="C82">
+        <v>5.13</v>
+      </c>
+      <c r="D82">
+        <v>3.38</v>
+      </c>
+      <c r="E82">
+        <v>6.65</v>
+      </c>
+      <c r="G82">
+        <v>1592</v>
+      </c>
+      <c r="H82">
+        <v>1754</v>
+      </c>
+      <c r="I82">
+        <v>1808</v>
+      </c>
+      <c r="K82">
+        <v>1429</v>
+      </c>
+      <c r="M82">
+        <v>85</v>
+      </c>
+      <c r="N82">
+        <v>93</v>
+      </c>
+      <c r="O82">
+        <v>84</v>
+      </c>
+      <c r="Q82">
+        <v>98</v>
+      </c>
+      <c r="S82">
+        <v>37</v>
+      </c>
+      <c r="T82">
+        <v>26</v>
+      </c>
+      <c r="U82">
+        <v>87</v>
+      </c>
+      <c r="W82">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83">
+        <v>4.05</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83">
+        <v>8.64</v>
+      </c>
+      <c r="E83" t="s">
+        <v>6</v>
+      </c>
+      <c r="F83">
+        <v>6.09</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1</v>
+      </c>
+      <c r="M85" t="s">
+        <v>2</v>
+      </c>
+      <c r="S85" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>10</v>
+      </c>
+      <c r="B86">
+        <v>7.54</v>
+      </c>
+      <c r="C86">
+        <v>7.54</v>
+      </c>
+      <c r="D86">
+        <v>8.1</v>
+      </c>
+      <c r="E86">
+        <v>8.64</v>
+      </c>
+      <c r="G86">
+        <v>586</v>
+      </c>
+      <c r="H86">
+        <v>1154</v>
+      </c>
+      <c r="I86">
+        <v>1227</v>
+      </c>
+      <c r="J86">
+        <v>994</v>
+      </c>
+      <c r="K86">
+        <v>845</v>
+      </c>
+      <c r="M86">
+        <v>123</v>
+      </c>
+      <c r="N86">
+        <v>97</v>
+      </c>
+      <c r="O86">
+        <v>89</v>
+      </c>
+      <c r="P86">
+        <v>107</v>
+      </c>
+      <c r="Q86">
+        <v>118</v>
+      </c>
+      <c r="S86">
+        <v>46</v>
+      </c>
+      <c r="T86">
+        <v>24</v>
+      </c>
+      <c r="U86">
+        <v>35</v>
+      </c>
+      <c r="V86">
+        <v>32</v>
+      </c>
+      <c r="W86">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>6.65</v>
+      </c>
+      <c r="B87">
+        <v>6.19</v>
+      </c>
+      <c r="C87">
+        <v>5.69</v>
+      </c>
+      <c r="D87">
+        <v>7.11</v>
+      </c>
+      <c r="E87">
+        <v>7.54</v>
+      </c>
+      <c r="G87">
+        <v>1375</v>
+      </c>
+      <c r="H87">
+        <v>1543</v>
+      </c>
+      <c r="I87">
+        <v>1641</v>
+      </c>
+      <c r="J87">
+        <v>1298</v>
+      </c>
+      <c r="K87">
+        <v>1219</v>
+      </c>
+      <c r="M87">
+        <v>89</v>
+      </c>
+      <c r="N87">
+        <v>101</v>
+      </c>
+      <c r="O87">
+        <v>102</v>
+      </c>
+      <c r="P87">
+        <v>90</v>
+      </c>
+      <c r="Q87">
+        <v>91</v>
+      </c>
+      <c r="S87">
+        <v>30</v>
+      </c>
+      <c r="T87">
+        <v>30</v>
+      </c>
+      <c r="U87">
+        <v>31</v>
+      </c>
+      <c r="V87">
+        <v>25</v>
+      </c>
+      <c r="W87">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>7.54</v>
+      </c>
+      <c r="B88">
+        <v>6.65</v>
+      </c>
+      <c r="C88">
+        <v>6.19</v>
+      </c>
+      <c r="D88">
+        <v>6.65</v>
+      </c>
+      <c r="E88">
+        <v>4.62</v>
+      </c>
+      <c r="G88">
+        <v>1217</v>
+      </c>
+      <c r="H88">
+        <v>1403</v>
+      </c>
+      <c r="I88">
+        <v>1494</v>
+      </c>
+      <c r="J88">
+        <v>1408</v>
+      </c>
+      <c r="M88">
+        <v>92</v>
+      </c>
+      <c r="N88">
+        <v>90</v>
+      </c>
+      <c r="O88">
+        <v>94</v>
+      </c>
+      <c r="P88">
+        <v>86</v>
+      </c>
+      <c r="S88">
+        <v>27</v>
+      </c>
+      <c r="T88">
+        <v>27</v>
+      </c>
+      <c r="U88">
+        <v>29</v>
+      </c>
+      <c r="V88">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89">
+        <v>5.69</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89">
+        <v>10</v>
+      </c>
+      <c r="E89" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>5.13</v>
+      </c>
+      <c r="B92">
+        <v>3.38</v>
+      </c>
+      <c r="C92">
+        <v>2.68</v>
+      </c>
+      <c r="D92">
+        <v>3.38</v>
+      </c>
+      <c r="E92">
+        <v>4.62</v>
+      </c>
+      <c r="G92">
+        <v>112.42</v>
+      </c>
+      <c r="H92">
+        <v>88.32</v>
+      </c>
+      <c r="I92">
+        <v>76.28</v>
+      </c>
+      <c r="J92">
+        <v>87.59</v>
+      </c>
+      <c r="K92">
+        <v>101.77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>3.38</v>
+      </c>
+      <c r="B93">
+        <v>2.68</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>3.38</v>
+      </c>
+      <c r="G93">
+        <v>83.89</v>
+      </c>
+      <c r="H93">
+        <v>73.17</v>
+      </c>
+      <c r="I93">
+        <v>68.290000000000006</v>
+      </c>
+      <c r="J93">
+        <v>68.98</v>
+      </c>
+      <c r="K93">
+        <v>88.93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>4.62</v>
+      </c>
+      <c r="B94">
+        <v>4.05</v>
+      </c>
+      <c r="C94">
+        <v>3.38</v>
+      </c>
+      <c r="D94">
+        <v>3.38</v>
+      </c>
+      <c r="E94">
+        <v>4.62</v>
+      </c>
+      <c r="G94">
+        <v>101.86</v>
+      </c>
+      <c r="H94">
+        <v>89.85</v>
+      </c>
+      <c r="I94">
+        <v>86.95</v>
+      </c>
+      <c r="J94">
+        <v>83.12</v>
+      </c>
+      <c r="K94">
+        <v>101.82</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A92:E94">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G92:K94">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -4339,7 +7956,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8:E10">
+  <conditionalFormatting sqref="A86:E88">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -4351,7 +7968,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:E4">
+  <conditionalFormatting sqref="A80:E82">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
